--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-06-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמוליק סוכות - נשאר רק הלב</v>
+        <v>תמר ריילי - מרים לי ברמות</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411271&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411289&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמוליק סוכות - נשאר רק הלב</v>
+        <v>תמר ריילי - מרים לי ברמות</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שלומי ימין - תודה על הכל</v>
+        <v>תמיר גל - דם זה לא מים</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411270&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411288&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שלומי ימין - תודה על הכל</v>
+        <v>תמיר גל - דם זה לא מים</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עידו כנפי - נגמרה המלחמה</v>
+        <v>שניר עוקשי - הבטחות גדולות</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411269&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411287&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>עידו כנפי - נגמרה המלחמה</v>
+        <v>שניר עוקשי - הבטחות גדולות</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מורן מצליח - אהבה בשתי שפות</v>
+        <v>שירי מימון &amp; עופר ניסים - תסתכל לי בעיניים</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411268&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411286&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מורן מצליח - אהבה בשתי שפות</v>
+        <v>שירי מימון &amp; עופר ניסים - תסתכל לי בעיניים</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יוסף חיים - טאטע תציל</v>
+        <v>שירז אברהם - את כל הזמן בוכה</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411267&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411285&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יוסף חיים - טאטע תציל</v>
+        <v>שירז אברהם - את כל הזמן בוכה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>בנימין משה - הכל היסטוריה</v>
+        <v>רועי לביא - פשוט יודע</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411266&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411284&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,12 +659,240 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>בנימין משה - הכל היסטוריה</v>
+        <v>רועי לביא - פשוט יודע</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>עדן בן זקן &amp; ששון שאולוב - מחול</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411283&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>עדן בן זקן &amp; ששון שאולוב - מחול</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>הראל מויאל - גיבור מנייר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411282&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>הראל מויאל - גיבור מנייר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אלדד ישעיהו - חי את החיים</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411281&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אלדד ישעיהו - חי את החיים</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אינו - מועדון הלבבות השבורים</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411280&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אינו - מועדון הלבבות השבורים</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אוהד שרגאי - נערי שובה אליי קאבר</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411279&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אוהד שרגאי - נערי שובה אליי קאבר</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אוהב חממה - אהבת חינם</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411278&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אוהב חממה - אהבת חינם</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-06-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תמר ריילי - מרים לי ברמות</v>
+        <v>מוטי כרמל &amp; אביה שרמן - קרוב אליך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411289&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411297&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-09</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תמר ריילי - מרים לי ברמות</v>
+        <v>מוטי כרמל &amp; אביה שרמן - קרוב אליך</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>תמיר גל - דם זה לא מים</v>
+        <v>ליאור מיארה - מחרוזת שבוי לאהבה 2026</v>
       </c>
       <c r="B3" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411288&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411296&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-09</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>תמיר גל - דם זה לא מים</v>
+        <v>ליאור מיארה - מחרוזת שבוי לאהבה 2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שניר עוקשי - הבטחות גדולות</v>
+        <v>ליאור מיארה - מחרוזת נשיקה 2026</v>
       </c>
       <c r="B4" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411287&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411295&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-09</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שניר עוקשי - הבטחות גדולות</v>
+        <v>ליאור מיארה - מחרוזת נשיקה 2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שירי מימון &amp; עופר ניסים - תסתכל לי בעיניים</v>
+        <v>יאיר בן טוב - מנסה</v>
       </c>
       <c r="B5" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411286&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411294&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D5" t="str">
         <v>2026-06-09</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שירי מימון &amp; עופר ניסים - תסתכל לי בעיניים</v>
+        <v>יאיר בן טוב - מנסה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>שירז אברהם - את כל הזמן בוכה</v>
+        <v>גוסטו - רוב הזמן את אשתי</v>
       </c>
       <c r="B6" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411285&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411293&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D6" t="str">
         <v>2026-06-09</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>שירז אברהם - את כל הזמן בוכה</v>
+        <v>גוסטו - רוב הזמן את אשתי</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>רועי לביא - פשוט יודע</v>
+        <v>אמיר שוהר - מסיבה של השמחות</v>
       </c>
       <c r="B7" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411284&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411292&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D7" t="str">
         <v>2026-06-09</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>רועי לביא - פשוט יודע</v>
+        <v>אמיר שוהר - מסיבה של השמחות</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>עדן בן זקן &amp; ששון שאולוב - מחול</v>
+        <v>אוהד חסקי &amp; אליף יילדיז - את בגדת בי</v>
       </c>
       <c r="B8" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411283&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411291&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D8" t="str">
         <v>2026-06-09</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>עדן בן זקן &amp; ששון שאולוב - מחול</v>
+        <v>אוהד חסקי &amp; אליף יילדיז - את בגדת בי</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>הראל מויאל - גיבור מנייר</v>
+        <v>אביתר גואטה - החטא שלי</v>
       </c>
       <c r="B9" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411282&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411290&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D9" t="str">
         <v>2026-06-09</v>
@@ -735,164 +735,12 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>הראל מויאל - גיבור מנייר</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אלדד ישעיהו - חי את החיים</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411281&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אלדד ישעיהו - חי את החיים</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אינו - מועדון הלבבות השבורים</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411280&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אינו - מועדון הלבבות השבורים</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אוהד שרגאי - נערי שובה אליי קאבר</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411279&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אוהד שרגאי - נערי שובה אליי קאבר</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>אוהב חממה - אהבת חינם</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411278&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>אוהב חממה - אהבת חינם</v>
+        <v>אביתר גואטה - החטא שלי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-06-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מוטי כרמל &amp; אביה שרמן - קרוב אליך</v>
+        <v>נועם אוחיון - אחת בלילה קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411297&amp;sid=55390b5eabec38928044626c162bd3cb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411314&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מוטי כרמל &amp; אביה שרמן - קרוב אליך</v>
+        <v>נועם אוחיון - אחת בלילה קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ליאור מיארה - מחרוזת שבוי לאהבה 2026</v>
+        <v>שרית אהרון - לומדת לנשום</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411296&amp;sid=55390b5eabec38928044626c162bd3cb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411313&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>ליאור מיארה - מחרוזת שבוי לאהבה 2026</v>
+        <v>שרית אהרון - לומדת לנשום</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ליאור מיארה - מחרוזת נשיקה 2026</v>
+        <v>רומי רון - בוחרים בטובים</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411295&amp;sid=55390b5eabec38928044626c162bd3cb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411312&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ליאור מיארה - מחרוזת נשיקה 2026</v>
+        <v>רומי רון - בוחרים בטובים</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יאיר בן טוב - מנסה</v>
+        <v>ראול - שיר לטל</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411294&amp;sid=55390b5eabec38928044626c162bd3cb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411311&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יאיר בן טוב - מנסה</v>
+        <v>ראול - שיר לטל</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>גוסטו - רוב הזמן את אשתי</v>
+        <v>עדן חסון - הלוואי שטוב לך</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411293&amp;sid=55390b5eabec38928044626c162bd3cb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411310&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>גוסטו - רוב הזמן את אשתי</v>
+        <v>עדן חסון - הלוואי שטוב לך</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אמיר שוהר - מסיבה של השמחות</v>
+        <v>נתי - עד שבאת</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411292&amp;sid=55390b5eabec38928044626c162bd3cb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411309&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אמיר שוהר - מסיבה של השמחות</v>
+        <v>נתי - עד שבאת</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אוהד חסקי &amp; אליף יילדיז - את בגדת בי</v>
+        <v>מתן אלדר - שוב</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411291&amp;sid=55390b5eabec38928044626c162bd3cb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411308&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אוהד חסקי &amp; אליף יילדיז - את בגדת בי</v>
+        <v>מתן אלדר - שוב</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אביתר גואטה - החטא שלי</v>
+        <v>יהונתן רייר - לשחרר</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411290&amp;sid=55390b5eabec38928044626c162bd3cb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411307&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,12 +735,354 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אביתר גואטה - החטא שלי</v>
+        <v>יהונתן רייר - לשחרר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>התקווה 6 &amp; סבא אורי (תמיר בר) - מכת זקנה</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411306&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>התקווה 6 &amp; סבא אורי (תמיר בר) - מכת זקנה</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אלי בי - הבימה</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411305&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אלי בי - הבימה</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אורן להב - מתעלייך</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411304&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אורן להב - מתעלייך</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אופירה שופן &amp; ינון יהל - גברים שלא נדע</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411303&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אופירה שופן &amp; ינון יהל - גברים שלא נדע</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>שר-אל - רק את</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411302&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>שר-אל - רק את</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>ראובן המלאך - נשבע לך</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411301&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>ראובן המלאך - נשבע לך</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>קובי ממן - חוף בגבעתיים</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411300&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>קובי ממן - חוף בגבעתיים</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>נס &amp; סטילה - מי כמוני</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411299&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>נס &amp; סטילה - מי כמוני</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>משה לוק - יה דודי</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411298&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>משה לוק - יה דודי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L18"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-06-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נועם אוחיון - אחת בלילה קאבר</v>
+        <v>תהילה עג'מי - לב סגור</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411314&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411329&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נועם אוחיון - אחת בלילה קאבר</v>
+        <v>תהילה עג'מי - לב סגור</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שרית אהרון - לומדת לנשום</v>
+        <v>רבי אלמוג אסלן - מחרוזת חסידית 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411313&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411328&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שרית אהרון - לומדת לנשום</v>
+        <v>רבי אלמוג אסלן - מחרוזת חסידית 2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>רומי רון - בוחרים בטובים</v>
+        <v>ניסים שומינוב - שתיקות ארוכות</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411312&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411327&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>רומי רון - בוחרים בטובים</v>
+        <v>ניסים שומינוב - שתיקות ארוכות</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ראול - שיר לטל</v>
+        <v>נטע ברזילי &amp; ניבר זנטי - ברבורה</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411311&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411326&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ראול - שיר לטל</v>
+        <v>נטע ברזילי &amp; ניבר זנטי - ברבורה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>עדן חסון - הלוואי שטוב לך</v>
+        <v>מתנאל סבח - קולו נדם</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411310&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411325&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>עדן חסון - הלוואי שטוב לך</v>
+        <v>מתנאל סבח - קולו נדם</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>נתי - עד שבאת</v>
+        <v>מתן דינו &amp; שפיטה &amp; נטלי פרץ - אין לך מילה 2</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411309&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411324&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>נתי - עד שבאת</v>
+        <v>מתן דינו &amp; שפיטה &amp; נטלי פרץ - אין לך מילה 2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>מתן אלדר - שוב</v>
+        <v>מאריאז' - הללויה תהילים קי''ז</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411308&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411323&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>מתן אלדר - שוב</v>
+        <v>מאריאז' - הללויה תהילים קי''ז</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>יהונתן רייר - לשחרר</v>
+        <v>ליאן ניגרין - מחרוזת עושה חיים 2026</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411307&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411322&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>יהונתן רייר - לשחרר</v>
+        <v>ליאן ניגרין - מחרוזת עושה חיים 2026</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>התקווה 6 &amp; סבא אורי (תמיר בר) - מכת זקנה</v>
+        <v>ליאל שרעבי - אחת למיליון</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411306&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411321&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>התקווה 6 &amp; סבא אורי (תמיר בר) - מכת זקנה</v>
+        <v>ליאל שרעבי - אחת למיליון</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אלי בי - הבימה</v>
+        <v>יוסף שושן - השדים שלך</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411305&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411320&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,21 +811,21 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אלי בי - הבימה</v>
+        <v>יוסף שושן - השדים שלך</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>אורן להב - מתעלייך</v>
+        <v>הודיה ויצמן - איך ממשיכים מכאן</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411304&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411319&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -849,21 +849,21 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>אורן להב - מתעלייך</v>
+        <v>הודיה ויצמן - איך ממשיכים מכאן</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>אופירה שופן &amp; ינון יהל - גברים שלא נדע</v>
+        <v>אלמוג טויטו &amp; יוני מאמוש - עברנו מלחמות נעבור את זה גם הורדה</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411303&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411318&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -887,21 +887,21 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>אופירה שופן &amp; ינון יהל - גברים שלא נדע</v>
+        <v>אלמוג טויטו &amp; יוני מאמוש - עברנו מלחמות נעבור את זה גם הורדה</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>שר-אל - רק את</v>
+        <v>אליהו חזן - מחרוזת ישמח חתני 2026</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411302&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411317&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -925,21 +925,21 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>שר-אל - רק את</v>
+        <v>אליהו חזן - מחרוזת ישמח חתני 2026</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ראובן המלאך - נשבע לך</v>
+        <v>אחיה טמיר - לוחם</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411301&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411316&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -963,21 +963,21 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>ראובן המלאך - נשבע לך</v>
+        <v>אחיה טמיר - לוחם</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>קובי ממן - חוף בגבעתיים</v>
+        <v>אושר ביטון - אושר שלי</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411300&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411315&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1001,88 +1001,12 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>קובי ממן - חוף בגבעתיים</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>נס &amp; סטילה - מי כמוני</v>
-      </c>
-      <c r="B17" t="str">
-        <v>2026-06-10</v>
-      </c>
-      <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411299&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
-      </c>
-      <c r="D17" t="str">
-        <v>2026-06-10</v>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J17" t="str">
-        <v/>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-      <c r="L17" t="str">
-        <v>נס &amp; סטילה - מי כמוני</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>משה לוק - יה דודי</v>
-      </c>
-      <c r="B18" t="str">
-        <v>2026-06-10</v>
-      </c>
-      <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411298&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
-      </c>
-      <c r="D18" t="str">
-        <v>2026-06-10</v>
-      </c>
-      <c r="E18" t="str">
-        <v/>
-      </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J18" t="str">
-        <v/>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str">
-        <v>משה לוק - יה דודי</v>
+        <v>אושר ביטון - אושר שלי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L16"/>
   </ignoredErrors>
 </worksheet>
 </file>